--- a/Grupo/US_Grupo.xlsx
+++ b/Grupo/US_Grupo.xlsx
@@ -458,16 +458,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>43.05446973756073</v>
+        <v>43.05446973756072</v>
       </c>
       <c r="C2" s="2">
-        <v>115.0810743115282</v>
+        <v>115.0992324889165</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>49.54754631311669</v>
+        <v>49.55536422010522</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -535,7 +535,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="2">
-        <v>3.548140672330238</v>
+        <v>3.548140672330237</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>5.549414135356372</v>
+        <v>5.549414135356373</v>
       </c>
       <c r="C11" s="2">
         <v>130.5758185417437</v>
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="2">
-        <v>7.246192931512813</v>
+        <v>7.246192931512815</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -645,7 +645,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="2">
-        <v>1.77731455466035</v>
+        <v>1.777314554660351</v>
       </c>
       <c r="C13" s="2">
         <v>101.7497573969899</v>
